--- a/JND_Study/JND_Data/2024-01-30_20-47.xlsx
+++ b/JND_Study/JND_Data/2024-01-30_20-47.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sreela/Documents/School/Stanford/Year3_2/PIEZO2/JND_Study/JND_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAD818C-9684-2144-83DF-10C24CCDDB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684F924A-DC86-1647-A156-A27435E38873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37980" yWindow="-500" windowWidth="26740" windowHeight="22000" xr2:uid="{1B4DE873-A15E-BD41-A0B0-8A0C0D8007DE}"/>
+    <workbookView xWindow="38480" yWindow="0" windowWidth="26740" windowHeight="22000" activeTab="1" xr2:uid="{1B4DE873-A15E-BD41-A0B0-8A0C0D8007DE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="trial" sheetId="1" r:id="rId1"/>
+    <sheet name="forceStaircase" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="trial_2024_01_30_20_47" localSheetId="0">Sheet1!$A$1:$I$51</definedName>
+    <definedName name="forceOfStairCase_onePoke_2024_01_30_20_47" localSheetId="1">forceStaircase!$A$1:$F$51</definedName>
+    <definedName name="trial_2024_01_30_20_47" localSheetId="0">trial!$A$1:$I$51</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +42,19 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{BC09CFE6-D28E-9E4E-B370-DFDD2A692B40}" name="trial_2024-01-30_20-47" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="1" xr16:uid="{A1876DE3-0C14-534A-A8BD-7A0D28632357}" name="forceOfStairCase_onePoke_2024-01-30_20-47" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/Sreela/Documents/School/Stanford/Year3_2/PIEZO2/JND_Study/JND_Data/forceOfStairCase_onePoke_2024-01-30_20-47.csv" comma="1">
+      <textFields count="6">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" xr16:uid="{BC09CFE6-D28E-9E4E-B370-DFDD2A692B40}" name="trial_2024-01-30_20-47" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="10000" sourceFile="/Users/Sreela/Documents/School/Stanford/Year3_2/PIEZO2/JND_Study/JND_Data/2024-01-30_20-47/trial_2024-01-30_20-47.csv" comma="1">
       <textFields count="9">
         <textField/>
@@ -59,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>trialCount</t>
   </si>
@@ -89,6 +103,21 @@
   </si>
   <si>
     <t>16 reversals</t>
+  </si>
+  <si>
+    <t>testCommand</t>
+  </si>
+  <si>
+    <t>meanForce</t>
+  </si>
+  <si>
+    <t>stdevForce</t>
+  </si>
+  <si>
+    <t>meanForce1</t>
+  </si>
+  <si>
+    <t>stdevForce1</t>
   </si>
 </sst>
 </file>
@@ -206,7 +235,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>trial!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -241,7 +270,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$51</c:f>
+              <c:f>trial!$B$2:$B$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -679,7 +708,7 @@
           </c:errBars>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$34:$R$34</c:f>
+              <c:f>trial!$Q$34:$R$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -695,6 +724,1600 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-A8F4-C040-8138-F22A3134256D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="867211807"/>
+        <c:axId val="928100447"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="867211807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="928100447"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="928100447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="867211807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>staircase actuator command (fixed) - 1 actuator</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>forceStaircase!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>testCommand</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>forceStaircase!$B$2:$B$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>94</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-15B7-F944-AC5E-7D630FAE0EB2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="972298207"/>
+        <c:axId val="915957391"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="972298207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="915957391"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="915957391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="90"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972298207"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>forceStaircase!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>meanForce</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>forceStaircase!$C$2:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>8.7906249999999897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5106249999999992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.1368749999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5818750000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.1216071428571404</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.8757446808510601</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.3344210526315701</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8617857142857099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.6312499999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.8205714285714203</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8205714285714203</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.7923684210526298</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.7923684210526298</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.8757446808510601</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.8757446808510601</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.3344210526315701</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.3344210526315701</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.8617857142857099</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.8235999999999901</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.8235999999999901</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.9072368421052603</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.9072368421052603</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.1216071428571404</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.1216071428571404</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.8757446808510601</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.8757446808510601</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.3344210526315701</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6.3344210526315701</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5.8617857142857099</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.8235999999999901</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.8235999999999901</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.8846551724137903</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.9072368421052603</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6.9072368421052603</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.7021739130434703</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.7923684210526298</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.7923684210526298</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.3185714285714196</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.3185714285714196</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.9319999999999897</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D390-3549-AEC6-9D13C2564735}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="830193167"/>
+        <c:axId val="830304911"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="830193167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="830304911"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="830304911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="830193167"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>forceStaircase!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>meanForce1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>forceStaircase!$E$2:$E$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>-1.213125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.1456249999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.0131250000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.73428571428571399</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.59680851063829699</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.57884210526315705</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.60482142857142795</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.578125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.78942857142857104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.78942857142857104</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.60539473684210499</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.60539473684210499</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.59680851063829699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.59680851063829699</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.57884210526315705</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.57884210526315705</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.60482142857142795</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.68613333333333304</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.68613333333333304</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.73723684210526297</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.73723684210526297</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.73428571428571399</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.73428571428571399</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.59680851063829699</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.59680851063829699</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.57884210526315705</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.57884210526315705</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.60482142857142795</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.68613333333333304</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.68613333333333304</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.78293103448275803</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.73723684210526297</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.73723684210526297</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-0.55469565217391203</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.60539473684210499</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.60539473684210499</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-0.49</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.49333333333333301</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4A93-9E43-8F1D-891D0EE6DF67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1062905391"/>
+        <c:axId val="1063052575"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1062905391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1063052575"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1063052575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1062905391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numLit>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numLit>
+            </c:plus>
+            <c:minus>
+              <c:numLit>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numLit>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:val>
+            <c:numRef>
+              <c:f>trial!$Q$34:$R$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>98.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>103.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-76B3-334D-9C20-111F29B6257B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -949,6 +2572,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -1453,6 +3236,2018 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1995,16 +5790,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>448791</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>123181</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>413267</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>185349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>67791</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>21581</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>32266</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>83749</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2032,8 +5827,163 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2409420-BF1E-0936-5143-D347A7995CA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D706CE7D-188C-D637-3A41-3C16D280F781}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{863086AA-108B-BA22-7A6B-8D7E4D901A06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>447164</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>116520</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D34FB0B7-5949-554A-B24F-1038E7B33EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="trial_2024-01-30_20-47" connectionId="1" xr16:uid="{07978A7D-3607-0841-BC9F-EED40D64B000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="trial_2024-01-30_20-47" connectionId="2" xr16:uid="{07978A7D-3607-0841-BC9F-EED40D64B000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="forceOfStairCase_onePoke_2024-01-30_20-47" connectionId="1" xr16:uid="{EDC64C12-E75F-1844-A114-7D2120A3FCE5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3956,4 +7906,1156 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A85C539-6AFE-FB41-8E42-621377AD1F9A}">
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>120</v>
+      </c>
+      <c r="C2">
+        <v>8.7906249999999897</v>
+      </c>
+      <c r="D2">
+        <v>0.502275680652567</v>
+      </c>
+      <c r="E2">
+        <v>-1.213125</v>
+      </c>
+      <c r="F2">
+        <v>0.101717669925141</v>
+      </c>
+      <c r="N2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>8.5106249999999992</v>
+      </c>
+      <c r="D3">
+        <v>0.170824059707642</v>
+      </c>
+      <c r="E3">
+        <v>-1.1456249999999999</v>
+      </c>
+      <c r="F3">
+        <v>2.1785531322416701E-2</v>
+      </c>
+      <c r="O3">
+        <f>O2+1</f>
+        <v>2</v>
+      </c>
+      <c r="P3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>114</v>
+      </c>
+      <c r="C4">
+        <v>8.1368749999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.106226100253186</v>
+      </c>
+      <c r="E4">
+        <v>-1.05</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4:O17" si="0">O3+1</f>
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>111</v>
+      </c>
+      <c r="C5">
+        <v>7.5818750000000001</v>
+      </c>
+      <c r="D5">
+        <v>5.7902801098047303E-2</v>
+      </c>
+      <c r="E5">
+        <v>-1.0131250000000001</v>
+      </c>
+      <c r="F5">
+        <v>7.3969482727676297E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>108</v>
+      </c>
+      <c r="C6">
+        <v>7.1216071428571404</v>
+      </c>
+      <c r="D6">
+        <v>1.38412269375859</v>
+      </c>
+      <c r="E6">
+        <v>-0.73428571428571399</v>
+      </c>
+      <c r="F6">
+        <v>0.19778105808892699</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>105</v>
+      </c>
+      <c r="C7">
+        <v>6.8757446808510601</v>
+      </c>
+      <c r="D7">
+        <v>1.1565313964533499</v>
+      </c>
+      <c r="E7">
+        <v>-0.59680851063829699</v>
+      </c>
+      <c r="F7">
+        <v>0.18599481098891699</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="P7">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>102</v>
+      </c>
+      <c r="C8">
+        <v>6.3344210526315701</v>
+      </c>
+      <c r="D8">
+        <v>1.2407185658144899</v>
+      </c>
+      <c r="E8">
+        <v>-0.57884210526315705</v>
+      </c>
+      <c r="F8">
+        <v>0.19349344152026701</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="P8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>99</v>
+      </c>
+      <c r="C9">
+        <v>5.8617857142857099</v>
+      </c>
+      <c r="D9">
+        <v>0.927881818103656</v>
+      </c>
+      <c r="E9">
+        <v>-0.60482142857142795</v>
+      </c>
+      <c r="F9">
+        <v>0.193833425094005</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>96</v>
+      </c>
+      <c r="C10">
+        <v>5.6312499999999996</v>
+      </c>
+      <c r="D10">
+        <v>4.3571062644833299E-2</v>
+      </c>
+      <c r="E10">
+        <v>-0.578125</v>
+      </c>
+      <c r="F10">
+        <v>9.7289436091489295E-2</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="P10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>101</v>
+      </c>
+      <c r="C11">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D11">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E11">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F11">
+        <v>0.19121218238394999</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D12">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E12">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F12">
+        <v>0.19121218238394999</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="P12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>98</v>
+      </c>
+      <c r="C13">
+        <v>5.8205714285714203</v>
+      </c>
+      <c r="D13">
+        <v>0.65065656008655803</v>
+      </c>
+      <c r="E13">
+        <v>-0.78942857142857104</v>
+      </c>
+      <c r="F13">
+        <v>0.108810263621534</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="P13">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>98</v>
+      </c>
+      <c r="C14">
+        <v>5.8205714285714203</v>
+      </c>
+      <c r="D14">
+        <v>0.65065656008655803</v>
+      </c>
+      <c r="E14">
+        <v>-0.78942857142857104</v>
+      </c>
+      <c r="F14">
+        <v>0.108810263621534</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="P14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>103</v>
+      </c>
+      <c r="C15">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D15">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E15">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F15">
+        <v>0.276126378561734</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="P15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>103</v>
+      </c>
+      <c r="C16">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D16">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E16">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F16">
+        <v>0.276126378561734</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="P16">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>5.7923684210526298</v>
+      </c>
+      <c r="D17">
+        <v>1.10944493995522</v>
+      </c>
+      <c r="E17">
+        <v>-0.60539473684210499</v>
+      </c>
+      <c r="F17">
+        <v>0.17685439141218001</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="P17">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>5.7923684210526298</v>
+      </c>
+      <c r="D18">
+        <v>1.10944493995522</v>
+      </c>
+      <c r="E18">
+        <v>-0.60539473684210499</v>
+      </c>
+      <c r="F18">
+        <v>0.17685439141218001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>105</v>
+      </c>
+      <c r="C19">
+        <v>6.8757446808510601</v>
+      </c>
+      <c r="D19">
+        <v>1.1565313964533499</v>
+      </c>
+      <c r="E19">
+        <v>-0.59680851063829699</v>
+      </c>
+      <c r="F19">
+        <v>0.18599481098891699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>105</v>
+      </c>
+      <c r="C20">
+        <v>6.8757446808510601</v>
+      </c>
+      <c r="D20">
+        <v>1.1565313964533499</v>
+      </c>
+      <c r="E20">
+        <v>-0.59680851063829699</v>
+      </c>
+      <c r="F20">
+        <v>0.18599481098891699</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>102</v>
+      </c>
+      <c r="C21">
+        <v>6.3344210526315701</v>
+      </c>
+      <c r="D21">
+        <v>1.2407185658144899</v>
+      </c>
+      <c r="E21">
+        <v>-0.57884210526315705</v>
+      </c>
+      <c r="F21">
+        <v>0.19349344152026701</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>102</v>
+      </c>
+      <c r="C22">
+        <v>6.3344210526315701</v>
+      </c>
+      <c r="D22">
+        <v>1.2407185658144899</v>
+      </c>
+      <c r="E22">
+        <v>-0.57884210526315705</v>
+      </c>
+      <c r="F22">
+        <v>0.19349344152026701</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>99</v>
+      </c>
+      <c r="C23">
+        <v>5.8617857142857099</v>
+      </c>
+      <c r="D23">
+        <v>0.927881818103656</v>
+      </c>
+      <c r="E23">
+        <v>-0.60482142857142795</v>
+      </c>
+      <c r="F23">
+        <v>0.193833425094005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>104</v>
+      </c>
+      <c r="C24">
+        <v>6.8235999999999901</v>
+      </c>
+      <c r="D24">
+        <v>1.2472504586756601</v>
+      </c>
+      <c r="E24">
+        <v>-0.68613333333333304</v>
+      </c>
+      <c r="F24">
+        <v>0.128248647382947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>104</v>
+      </c>
+      <c r="C25">
+        <v>6.8235999999999901</v>
+      </c>
+      <c r="D25">
+        <v>1.2472504586756601</v>
+      </c>
+      <c r="E25">
+        <v>-0.68613333333333304</v>
+      </c>
+      <c r="F25">
+        <v>0.128248647382947</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>101</v>
+      </c>
+      <c r="C26">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D26">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E26">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F26">
+        <v>0.19121218238394999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>101</v>
+      </c>
+      <c r="C27">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D27">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E27">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F27">
+        <v>0.19121218238394999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>106</v>
+      </c>
+      <c r="C28">
+        <v>6.9072368421052603</v>
+      </c>
+      <c r="D28">
+        <v>1.4100565485900201</v>
+      </c>
+      <c r="E28">
+        <v>-0.73723684210526297</v>
+      </c>
+      <c r="F28">
+        <v>0.247022259194178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>106</v>
+      </c>
+      <c r="C29">
+        <v>6.9072368421052603</v>
+      </c>
+      <c r="D29">
+        <v>1.4100565485900201</v>
+      </c>
+      <c r="E29">
+        <v>-0.73723684210526297</v>
+      </c>
+      <c r="F29">
+        <v>0.247022259194178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>103</v>
+      </c>
+      <c r="C30">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D30">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E30">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F30">
+        <v>0.276126378561734</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>103</v>
+      </c>
+      <c r="C31">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D31">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E31">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F31">
+        <v>0.276126378561734</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>108</v>
+      </c>
+      <c r="C32">
+        <v>7.1216071428571404</v>
+      </c>
+      <c r="D32">
+        <v>1.38412269375859</v>
+      </c>
+      <c r="E32">
+        <v>-0.73428571428571399</v>
+      </c>
+      <c r="F32">
+        <v>0.19778105808892699</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>108</v>
+      </c>
+      <c r="C33">
+        <v>7.1216071428571404</v>
+      </c>
+      <c r="D33">
+        <v>1.38412269375859</v>
+      </c>
+      <c r="E33">
+        <v>-0.73428571428571399</v>
+      </c>
+      <c r="F33">
+        <v>0.19778105808892699</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>6.8757446808510601</v>
+      </c>
+      <c r="D34">
+        <v>1.1565313964533499</v>
+      </c>
+      <c r="E34">
+        <v>-0.59680851063829699</v>
+      </c>
+      <c r="F34">
+        <v>0.18599481098891699</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>105</v>
+      </c>
+      <c r="C35">
+        <v>6.8757446808510601</v>
+      </c>
+      <c r="D35">
+        <v>1.1565313964533499</v>
+      </c>
+      <c r="E35">
+        <v>-0.59680851063829699</v>
+      </c>
+      <c r="F35">
+        <v>0.18599481098891699</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>102</v>
+      </c>
+      <c r="C36">
+        <v>6.3344210526315701</v>
+      </c>
+      <c r="D36">
+        <v>1.2407185658144899</v>
+      </c>
+      <c r="E36">
+        <v>-0.57884210526315705</v>
+      </c>
+      <c r="F36">
+        <v>0.19349344152026701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>102</v>
+      </c>
+      <c r="C37">
+        <v>6.3344210526315701</v>
+      </c>
+      <c r="D37">
+        <v>1.2407185658144899</v>
+      </c>
+      <c r="E37">
+        <v>-0.57884210526315705</v>
+      </c>
+      <c r="F37">
+        <v>0.19349344152026701</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>99</v>
+      </c>
+      <c r="C38">
+        <v>5.8617857142857099</v>
+      </c>
+      <c r="D38">
+        <v>0.927881818103656</v>
+      </c>
+      <c r="E38">
+        <v>-0.60482142857142795</v>
+      </c>
+      <c r="F38">
+        <v>0.193833425094005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>104</v>
+      </c>
+      <c r="C39">
+        <v>6.8235999999999901</v>
+      </c>
+      <c r="D39">
+        <v>1.2472504586756601</v>
+      </c>
+      <c r="E39">
+        <v>-0.68613333333333304</v>
+      </c>
+      <c r="F39">
+        <v>0.128248647382947</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>104</v>
+      </c>
+      <c r="C40">
+        <v>6.8235999999999901</v>
+      </c>
+      <c r="D40">
+        <v>1.2472504586756601</v>
+      </c>
+      <c r="E40">
+        <v>-0.68613333333333304</v>
+      </c>
+      <c r="F40">
+        <v>0.128248647382947</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D41">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E41">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F41">
+        <v>0.19121218238394999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>101</v>
+      </c>
+      <c r="C42">
+        <v>5.8846551724137903</v>
+      </c>
+      <c r="D42">
+        <v>1.1806824670462699</v>
+      </c>
+      <c r="E42">
+        <v>-0.78293103448275803</v>
+      </c>
+      <c r="F42">
+        <v>0.19121218238394999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>106</v>
+      </c>
+      <c r="C43">
+        <v>6.9072368421052603</v>
+      </c>
+      <c r="D43">
+        <v>1.4100565485900201</v>
+      </c>
+      <c r="E43">
+        <v>-0.73723684210526297</v>
+      </c>
+      <c r="F43">
+        <v>0.247022259194178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>106</v>
+      </c>
+      <c r="C44">
+        <v>6.9072368421052603</v>
+      </c>
+      <c r="D44">
+        <v>1.4100565485900201</v>
+      </c>
+      <c r="E44">
+        <v>-0.73723684210526297</v>
+      </c>
+      <c r="F44">
+        <v>0.247022259194178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>103</v>
+      </c>
+      <c r="C45">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D45">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E45">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F45">
+        <v>0.276126378561734</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>103</v>
+      </c>
+      <c r="C46">
+        <v>6.7021739130434703</v>
+      </c>
+      <c r="D46">
+        <v>1.1937618891617801</v>
+      </c>
+      <c r="E46">
+        <v>-0.55469565217391203</v>
+      </c>
+      <c r="F46">
+        <v>0.276126378561734</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
+      </c>
+      <c r="C47">
+        <v>5.7923684210526298</v>
+      </c>
+      <c r="D47">
+        <v>1.10944493995522</v>
+      </c>
+      <c r="E47">
+        <v>-0.60539473684210499</v>
+      </c>
+      <c r="F47">
+        <v>0.17685439141218001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
+      </c>
+      <c r="C48">
+        <v>5.7923684210526298</v>
+      </c>
+      <c r="D48">
+        <v>1.10944493995522</v>
+      </c>
+      <c r="E48">
+        <v>-0.60539473684210499</v>
+      </c>
+      <c r="F48">
+        <v>0.17685439141218001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>97</v>
+      </c>
+      <c r="C49">
+        <v>5.3185714285714196</v>
+      </c>
+      <c r="D49">
+        <v>0.57356600246499401</v>
+      </c>
+      <c r="E49">
+        <v>-0.49</v>
+      </c>
+      <c r="F49">
+        <v>0.125811650607451</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>97</v>
+      </c>
+      <c r="C50">
+        <v>5.3185714285714196</v>
+      </c>
+      <c r="D50">
+        <v>0.57356600246499401</v>
+      </c>
+      <c r="E50">
+        <v>-0.49</v>
+      </c>
+      <c r="F50">
+        <v>0.125811650607451</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>94</v>
+      </c>
+      <c r="C51">
+        <v>4.9319999999999897</v>
+      </c>
+      <c r="D51">
+        <v>7.9598994968529402E-2</v>
+      </c>
+      <c r="E51">
+        <v>-0.49333333333333301</v>
+      </c>
+      <c r="F51">
+        <v>7.7344826732123603E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>